--- a/Results_experiment/exp_5/preds_1111113333322222.xlsx
+++ b/Results_experiment/exp_5/preds_1111113333322222.xlsx
@@ -990,7 +990,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D2">
-        <v>0.7436200976371765</v>
+        <v>1.057070016860962</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1004,7 +1004,7 @@
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>1.891591787338257</v>
+        <v>2.71083402633667</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1018,7 +1018,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D4">
-        <v>2.347784996032715</v>
+        <v>2.215957164764404</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1032,7 +1032,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D5">
-        <v>2.548388957977295</v>
+        <v>3.229129552841187</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1046,7 +1046,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D6">
-        <v>2.11862850189209</v>
+        <v>2.239906072616577</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1060,7 +1060,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D7">
-        <v>1.700188636779785</v>
+        <v>2.849609613418579</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1074,7 +1074,7 @@
         <v>3</v>
       </c>
       <c r="D8">
-        <v>3.204753398895264</v>
+        <v>3.019400835037231</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1088,7 +1088,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D9">
-        <v>9.043307304382324</v>
+        <v>11.57494640350342</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1102,7 +1102,7 @@
         <v>7</v>
       </c>
       <c r="D10">
-        <v>3.325324773788452</v>
+        <v>3.232601881027222</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1116,7 +1116,7 @@
         <v>2.5</v>
       </c>
       <c r="D11">
-        <v>3.028776884078979</v>
+        <v>3.064547300338745</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1130,7 +1130,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D12">
-        <v>2.729974508285522</v>
+        <v>2.39959192276001</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1144,7 +1144,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D13">
-        <v>3.260570764541626</v>
+        <v>2.482740640640259</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1158,7 +1158,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D14">
-        <v>2.096390247344971</v>
+        <v>1.887576818466187</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1172,7 +1172,7 @@
         <v>6.5</v>
       </c>
       <c r="D15">
-        <v>3.160778760910034</v>
+        <v>2.226288795471191</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1186,7 +1186,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D16">
-        <v>3.075074434280396</v>
+        <v>2.432146072387695</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1200,7 +1200,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D17">
-        <v>3.596707820892334</v>
+        <v>4.012283325195312</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1214,7 +1214,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D18">
-        <v>2.428996324539185</v>
+        <v>2.821942567825317</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1228,7 +1228,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D19">
-        <v>7.378379344940186</v>
+        <v>7.667614936828613</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1242,7 +1242,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D20">
-        <v>2.921884536743164</v>
+        <v>2.867623805999756</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1256,7 +1256,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D21">
-        <v>2.509783744812012</v>
+        <v>2.839292764663696</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1270,7 +1270,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D22">
-        <v>2.243688583374023</v>
+        <v>2.171144247055054</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1284,7 +1284,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D23">
-        <v>2.306318044662476</v>
+        <v>2.138683795928955</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1298,7 +1298,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D24">
-        <v>3.185412645339966</v>
+        <v>3.243191719055176</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1312,7 +1312,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D25">
-        <v>2.265763759613037</v>
+        <v>2.180066347122192</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1326,7 +1326,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D26">
-        <v>2.868653059005737</v>
+        <v>2.455428123474121</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1340,7 +1340,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D27">
-        <v>3.129241943359375</v>
+        <v>2.956886529922485</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="D28">
-        <v>2.276979446411133</v>
+        <v>2.206782817840576</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1368,7 +1368,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D29">
-        <v>2.281841993331909</v>
+        <v>2.212656259536743</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1382,7 +1382,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D30">
-        <v>2.856547832489014</v>
+        <v>3.319722414016724</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1396,7 +1396,7 @@
         <v>1.5</v>
       </c>
       <c r="D31">
-        <v>3.503450632095337</v>
+        <v>3.592748880386353</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1410,7 +1410,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D32">
-        <v>3.175416469573975</v>
+        <v>3.540071725845337</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1424,7 +1424,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D33">
-        <v>3.084404706954956</v>
+        <v>2.52687668800354</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1438,7 +1438,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D34">
-        <v>8.666473388671875</v>
+        <v>6.351652145385742</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1452,7 +1452,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D35">
-        <v>4.064085960388184</v>
+        <v>3.228204727172852</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1466,7 +1466,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D36">
-        <v>2.910242795944214</v>
+        <v>2.483544111251831</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1480,7 +1480,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D37">
-        <v>3.027522802352905</v>
+        <v>2.356694221496582</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1494,7 +1494,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D38">
-        <v>2.717900514602661</v>
+        <v>2.181060314178467</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1508,7 +1508,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D39">
-        <v>2.805228471755981</v>
+        <v>1.434251308441162</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1522,7 +1522,7 @@
         <v>1</v>
       </c>
       <c r="D40">
-        <v>5.085068225860596</v>
+        <v>4.247959613800049</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1536,7 +1536,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D41">
-        <v>3.776278018951416</v>
+        <v>3.553364992141724</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1550,7 +1550,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D42">
-        <v>2.408714056015015</v>
+        <v>2.344521284103394</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1564,7 +1564,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D43">
-        <v>3.071294069290161</v>
+        <v>2.454548358917236</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1578,7 +1578,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D44">
-        <v>1.911522388458252</v>
+        <v>2.057764291763306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1592,7 +1592,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D45">
-        <v>1.33611011505127</v>
+        <v>2.046900510787964</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1606,7 +1606,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D46">
-        <v>2.331315755844116</v>
+        <v>2.052456855773926</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1620,7 +1620,7 @@
         <v>19.5</v>
       </c>
       <c r="D47">
-        <v>18.51752471923828</v>
+        <v>15.98790454864502</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1634,7 +1634,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D48">
-        <v>2.665517091751099</v>
+        <v>2.960966825485229</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1648,7 +1648,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D49">
-        <v>3.663384199142456</v>
+        <v>2.947580337524414</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1662,7 +1662,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D50">
-        <v>1.425378084182739</v>
+        <v>1.473375082015991</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1676,7 +1676,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D51">
-        <v>7.773925304412842</v>
+        <v>9.070549964904785</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1690,7 +1690,7 @@
         <v>16.10000038146973</v>
       </c>
       <c r="D52">
-        <v>15.83292388916016</v>
+        <v>13.98466491699219</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1704,7 +1704,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D53">
-        <v>1.016855239868164</v>
+        <v>1.449781537055969</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1718,7 +1718,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D54">
-        <v>4.581093788146973</v>
+        <v>3.900668859481812</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1732,7 +1732,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D55">
-        <v>2.78119683265686</v>
+        <v>2.488015174865723</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1746,7 +1746,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D56">
-        <v>3.465946912765503</v>
+        <v>3.875412702560425</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1760,7 +1760,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D57">
-        <v>2.310388088226318</v>
+        <v>2.209871768951416</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1774,7 +1774,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D58">
-        <v>2.910342216491699</v>
+        <v>2.929066896438599</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1788,7 +1788,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D59">
-        <v>2.057877540588379</v>
+        <v>2.28930139541626</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1802,7 +1802,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D60">
-        <v>2.336065530776978</v>
+        <v>2.103780746459961</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1816,7 +1816,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D61">
-        <v>3.458183288574219</v>
+        <v>3.016309976577759</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1830,7 +1830,7 @@
         <v>1.5</v>
       </c>
       <c r="D62">
-        <v>2.140846729278564</v>
+        <v>2.00065016746521</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -1844,7 +1844,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D63">
-        <v>3.392239093780518</v>
+        <v>3.066109180450439</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1858,7 +1858,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D64">
-        <v>8.136660575866699</v>
+        <v>6.164521217346191</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -1872,7 +1872,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D65">
-        <v>3.211908340454102</v>
+        <v>2.337981700897217</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1886,7 +1886,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D66">
-        <v>2.046970844268799</v>
+        <v>2.805046558380127</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1900,7 +1900,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D67">
-        <v>2.342981338500977</v>
+        <v>2.273088216781616</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1914,7 +1914,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D68">
-        <v>4.064033508300781</v>
+        <v>3.72894287109375</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1928,7 +1928,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D69">
-        <v>1.169723987579346</v>
+        <v>1.515399694442749</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1942,7 +1942,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D70">
-        <v>1.808295726776123</v>
+        <v>4.974950313568115</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -1956,7 +1956,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D71">
-        <v>3.165684700012207</v>
+        <v>3.053360939025879</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -1970,7 +1970,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D72">
-        <v>1.74189281463623</v>
+        <v>2.12978720664978</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1984,7 +1984,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D73">
-        <v>3.032178640365601</v>
+        <v>3.410794019699097</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1998,7 +1998,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D74">
-        <v>3.462800741195679</v>
+        <v>2.498618364334106</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2012,7 +2012,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D75">
-        <v>2.097133874893188</v>
+        <v>2.044111251831055</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2026,7 +2026,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D76">
-        <v>2.321194410324097</v>
+        <v>2.80186128616333</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2040,7 +2040,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D77">
-        <v>3.45067834854126</v>
+        <v>3.528450727462769</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2054,7 +2054,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D78">
-        <v>3.755080223083496</v>
+        <v>3.378250360488892</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2068,7 +2068,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D79">
-        <v>2.549028396606445</v>
+        <v>2.228277206420898</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2082,7 +2082,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D80">
-        <v>4.205963134765625</v>
+        <v>4.051295757293701</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2096,7 +2096,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D81">
-        <v>3.999800443649292</v>
+        <v>3.932379007339478</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2110,7 +2110,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D82">
-        <v>2.554475784301758</v>
+        <v>2.38932204246521</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2124,7 +2124,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D83">
-        <v>3.788329362869263</v>
+        <v>3.604349851608276</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2138,7 +2138,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D84">
-        <v>3.031389474868774</v>
+        <v>3.029380321502686</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2152,7 +2152,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D85">
-        <v>7.227147579193115</v>
+        <v>5.590376377105713</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2166,7 +2166,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D86">
-        <v>2.872395753860474</v>
+        <v>2.343205690383911</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2180,7 +2180,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D87">
-        <v>3.17213249206543</v>
+        <v>2.789172410964966</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2194,7 +2194,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D88">
-        <v>2.748650789260864</v>
+        <v>2.954131603240967</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2208,7 +2208,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D89">
-        <v>1.711590051651001</v>
+        <v>2.423932075500488</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2222,7 +2222,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D90">
-        <v>3.170011043548584</v>
+        <v>2.834224224090576</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2236,7 +2236,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D91">
-        <v>2.560261726379395</v>
+        <v>2.629188776016235</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2250,7 +2250,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D92">
-        <v>2.035337924957275</v>
+        <v>2.169522762298584</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2264,7 +2264,7 @@
         <v>0.5</v>
       </c>
       <c r="D93">
-        <v>2.164269208908081</v>
+        <v>2.175895690917969</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2278,7 +2278,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D94">
-        <v>3.753469705581665</v>
+        <v>3.511342287063599</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2292,7 +2292,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D95">
-        <v>2.135097742080688</v>
+        <v>1.381136417388916</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2306,7 +2306,7 @@
         <v>5</v>
       </c>
       <c r="D96">
-        <v>0.9357573986053467</v>
+        <v>2.081459045410156</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2320,7 +2320,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D97">
-        <v>2.197630405426025</v>
+        <v>2.23189902305603</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2334,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="D98">
-        <v>1.703789710998535</v>
+        <v>2.111971139907837</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2348,7 +2348,7 @@
         <v>3</v>
       </c>
       <c r="D99">
-        <v>2.638628721237183</v>
+        <v>3.283118009567261</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2362,7 +2362,7 @@
         <v>8.199999809265137</v>
       </c>
       <c r="D100">
-        <v>7.050593852996826</v>
+        <v>6.255898475646973</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2376,7 +2376,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D101">
-        <v>3.267569303512573</v>
+        <v>2.433912038803101</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2390,7 +2390,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D102">
-        <v>3.502551317214966</v>
+        <v>3.636426687240601</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2404,7 +2404,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D103">
-        <v>5.044162273406982</v>
+        <v>4.3349609375</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2418,7 +2418,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D104">
-        <v>3.890022993087769</v>
+        <v>3.631296157836914</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2432,7 +2432,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D105">
-        <v>2.929536581039429</v>
+        <v>2.461681127548218</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2446,7 +2446,7 @@
         <v>3</v>
       </c>
       <c r="D106">
-        <v>2.005094051361084</v>
+        <v>1.907279014587402</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2460,7 +2460,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D107">
-        <v>2.462347507476807</v>
+        <v>2.370463609695435</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2474,7 +2474,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D108">
-        <v>3.372176170349121</v>
+        <v>2.750774621963501</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2488,7 +2488,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D109">
-        <v>3.785771131515503</v>
+        <v>3.674665689468384</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2502,7 +2502,7 @@
         <v>31</v>
       </c>
       <c r="D110">
-        <v>25.39080810546875</v>
+        <v>25.0909538269043</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2516,7 +2516,7 @@
         <v>5</v>
       </c>
       <c r="D111">
-        <v>3.319758653640747</v>
+        <v>3.009769439697266</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2530,7 +2530,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D112">
-        <v>13.97616767883301</v>
+        <v>12.61440563201904</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2544,7 +2544,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D113">
-        <v>4.241896152496338</v>
+        <v>3.871949911117554</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2558,7 +2558,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D114">
-        <v>2.192507028579712</v>
+        <v>2.080702543258667</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2572,7 +2572,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D115">
-        <v>1.504765272140503</v>
+        <v>2.214954614639282</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2586,7 +2586,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D116">
-        <v>3.699758768081665</v>
+        <v>3.373947858810425</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2600,7 +2600,7 @@
         <v>3</v>
       </c>
       <c r="D117">
-        <v>2.200746774673462</v>
+        <v>2.951581239700317</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2614,7 +2614,7 @@
         <v>7.5</v>
       </c>
       <c r="D118">
-        <v>3.446930885314941</v>
+        <v>3.824623346328735</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2628,7 +2628,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D119">
-        <v>2.023939371109009</v>
+        <v>2.373857975006104</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2642,7 +2642,7 @@
         <v>3.5</v>
       </c>
       <c r="D120">
-        <v>2.443232774734497</v>
+        <v>2.499908685684204</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2656,7 +2656,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D121">
-        <v>3.417393922805786</v>
+        <v>3.168229818344116</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2670,7 +2670,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D122">
-        <v>3.451017141342163</v>
+        <v>2.978146314620972</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2684,7 +2684,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D123">
-        <v>2.993370771408081</v>
+        <v>3.016767740249634</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2698,7 +2698,7 @@
         <v>1.5</v>
       </c>
       <c r="D124">
-        <v>2.743019342422485</v>
+        <v>2.526501417160034</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2712,7 +2712,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D125">
-        <v>3.124978542327881</v>
+        <v>3.683156251907349</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2726,7 +2726,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D126">
-        <v>2.969823122024536</v>
+        <v>2.368289947509766</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2740,7 +2740,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D127">
-        <v>9.365156173706055</v>
+        <v>7.505138397216797</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2754,7 +2754,7 @@
         <v>20.20000076293945</v>
       </c>
       <c r="D128">
-        <v>16.35959434509277</v>
+        <v>16.17777633666992</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2768,7 +2768,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D129">
-        <v>1.9010009765625</v>
+        <v>1.850969552993774</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2782,7 +2782,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D130">
-        <v>1.976064443588257</v>
+        <v>1.206796407699585</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2796,7 +2796,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D131">
-        <v>0.9700351357460022</v>
+        <v>1.86077094078064</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2810,7 +2810,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D132">
-        <v>2.781409025192261</v>
+        <v>1.966148138046265</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -2824,7 +2824,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D133">
-        <v>1.994152069091797</v>
+        <v>2.349745988845825</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -2838,7 +2838,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D134">
-        <v>6.192304134368896</v>
+        <v>6.362384796142578</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2852,7 +2852,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D135">
-        <v>2.144999027252197</v>
+        <v>3.01004433631897</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -2866,7 +2866,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D136">
-        <v>2.402579545974731</v>
+        <v>2.88885760307312</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -2880,7 +2880,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D137">
-        <v>3.009638071060181</v>
+        <v>2.884004592895508</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2894,7 +2894,7 @@
         <v>9.300000190734863</v>
       </c>
       <c r="D138">
-        <v>5.334129810333252</v>
+        <v>3.980301141738892</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -2908,7 +2908,7 @@
         <v>32.20000076293945</v>
       </c>
       <c r="D139">
-        <v>25.69259262084961</v>
+        <v>24.75522232055664</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -2922,7 +2922,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D140">
-        <v>3.076532125473022</v>
+        <v>2.799455404281616</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -2936,7 +2936,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D141">
-        <v>5.739141941070557</v>
+        <v>5.971691608428955</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -2950,7 +2950,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D142">
-        <v>2.725683450698853</v>
+        <v>2.874318361282349</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -2964,7 +2964,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D143">
-        <v>2.014451026916504</v>
+        <v>2.021816730499268</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -2978,7 +2978,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D144">
-        <v>1.736911296844482</v>
+        <v>0.5382165312767029</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -2992,7 +2992,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D145">
-        <v>1.735808610916138</v>
+        <v>2.06829309463501</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3006,7 +3006,7 @@
         <v>23.20000076293945</v>
       </c>
       <c r="D146">
-        <v>18.74929618835449</v>
+        <v>19.25801086425781</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3020,7 +3020,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D147">
-        <v>2.746322870254517</v>
+        <v>2.318307876586914</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3034,7 +3034,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D148">
-        <v>1.895668268203735</v>
+        <v>1.838245868682861</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3048,7 +3048,7 @@
         <v>2</v>
       </c>
       <c r="D149">
-        <v>3.019294023513794</v>
+        <v>2.255972385406494</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3062,7 +3062,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D150">
-        <v>1.986254930496216</v>
+        <v>2.860195636749268</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3076,7 +3076,7 @@
         <v>5.5</v>
       </c>
       <c r="D151">
-        <v>0.9531410932540894</v>
+        <v>2.00897741317749</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3090,7 +3090,7 @@
         <v>4</v>
       </c>
       <c r="D152">
-        <v>2.798397541046143</v>
+        <v>2.412667036056519</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3104,7 +3104,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D153">
-        <v>2.813387632369995</v>
+        <v>2.390109300613403</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3118,7 +3118,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D154">
-        <v>4.797122478485107</v>
+        <v>4.793808937072754</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3132,7 +3132,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D155">
-        <v>2.712357044219971</v>
+        <v>2.44101095199585</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3146,7 +3146,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D156">
-        <v>2.974107503890991</v>
+        <v>4.29897928237915</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3160,7 +3160,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D157">
-        <v>11.06216812133789</v>
+        <v>10.42599582672119</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3174,7 +3174,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D158">
-        <v>1.871807813644409</v>
+        <v>2.262094497680664</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3188,7 +3188,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D159">
-        <v>1.435470342636108</v>
+        <v>1.049650907516479</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3202,7 +3202,7 @@
         <v>3.5</v>
       </c>
       <c r="D160">
-        <v>2.953584909439087</v>
+        <v>2.969030380249023</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3216,7 +3216,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D161">
-        <v>1.692679643630981</v>
+        <v>2.084712743759155</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3230,7 +3230,7 @@
         <v>3.5</v>
       </c>
       <c r="D162">
-        <v>2.621061325073242</v>
+        <v>2.397799730300903</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3244,7 +3244,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D163">
-        <v>2.168838739395142</v>
+        <v>2.25014328956604</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3258,7 +3258,7 @@
         <v>1.5</v>
       </c>
       <c r="D164">
-        <v>2.737177610397339</v>
+        <v>2.318080902099609</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3272,7 +3272,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D165">
-        <v>18.43023490905762</v>
+        <v>17.2972297668457</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3286,7 +3286,7 @@
         <v>1</v>
       </c>
       <c r="D166">
-        <v>2.239017248153687</v>
+        <v>2.116404056549072</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3300,7 +3300,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D167">
-        <v>3.481614589691162</v>
+        <v>3.935442924499512</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3314,7 +3314,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D168">
-        <v>2.24726676940918</v>
+        <v>2.28770923614502</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3328,7 +3328,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D169">
-        <v>3.070956707000732</v>
+        <v>3.000556230545044</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3342,7 +3342,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D170">
-        <v>1.567764282226562</v>
+        <v>2.049917221069336</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3356,7 +3356,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D171">
-        <v>1.955432891845703</v>
+        <v>3.04242467880249</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3370,7 +3370,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D172">
-        <v>3.190091133117676</v>
+        <v>3.064591646194458</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3384,7 +3384,7 @@
         <v>3.5</v>
       </c>
       <c r="D173">
-        <v>1.950213432312012</v>
+        <v>0.5369871258735657</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3398,7 +3398,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D174">
-        <v>2.165220737457275</v>
+        <v>2.697297334671021</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3412,7 +3412,7 @@
         <v>21.10000038146973</v>
       </c>
       <c r="D175">
-        <v>13.51830863952637</v>
+        <v>17.24556350708008</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3426,7 +3426,7 @@
         <v>5.5</v>
       </c>
       <c r="D176">
-        <v>3.020739316940308</v>
+        <v>2.915629148483276</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3440,7 +3440,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D177">
-        <v>1.825976371765137</v>
+        <v>2.364686489105225</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3454,7 +3454,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D178">
-        <v>1.369613647460938</v>
+        <v>1.87547755241394</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3468,7 +3468,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D179">
-        <v>3.90848970413208</v>
+        <v>3.470834255218506</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3482,7 +3482,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D180">
-        <v>3.425545454025269</v>
+        <v>3.34072470664978</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3496,7 +3496,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D181">
-        <v>1.011900663375854</v>
+        <v>0.5948068499565125</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3510,7 +3510,7 @@
         <v>1</v>
       </c>
       <c r="D182">
-        <v>1.945801973342896</v>
+        <v>2.037018537521362</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3524,7 +3524,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D183">
-        <v>8.00567626953125</v>
+        <v>5.303492546081543</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3538,7 +3538,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D184">
-        <v>2.274160146713257</v>
+        <v>3.13784384727478</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3552,7 +3552,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D185">
-        <v>2.455399513244629</v>
+        <v>2.319412231445312</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3566,7 +3566,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D186">
-        <v>3.864104986190796</v>
+        <v>2.985615968704224</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3580,7 +3580,7 @@
         <v>0.5</v>
       </c>
       <c r="D187">
-        <v>3.722348213195801</v>
+        <v>2.998462677001953</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3594,7 +3594,7 @@
         <v>7</v>
       </c>
       <c r="D188">
-        <v>3.742003202438354</v>
+        <v>3.697537422180176</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3608,7 +3608,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D189">
-        <v>2.483968734741211</v>
+        <v>2.334433317184448</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3622,7 +3622,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D190">
-        <v>2.433727264404297</v>
+        <v>2.373869180679321</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3636,7 +3636,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D191">
-        <v>3.448760747909546</v>
+        <v>3.364913940429688</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3650,7 +3650,7 @@
         <v>5.5</v>
       </c>
       <c r="D192">
-        <v>4.198643207550049</v>
+        <v>4.216666221618652</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3664,7 +3664,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D193">
-        <v>2.348094940185547</v>
+        <v>2.394444465637207</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3678,7 +3678,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D194">
-        <v>3.003770589828491</v>
+        <v>2.906018018722534</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3692,7 +3692,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D195">
-        <v>3.339058637619019</v>
+        <v>3.355253458023071</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3706,7 +3706,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D196">
-        <v>4.337488174438477</v>
+        <v>4.000339031219482</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3720,7 +3720,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D197">
-        <v>6.110281467437744</v>
+        <v>4.763857841491699</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3734,7 +3734,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D198">
-        <v>2.992818593978882</v>
+        <v>2.295450925827026</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3748,7 +3748,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D199">
-        <v>2.318818330764771</v>
+        <v>2.381197690963745</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3762,7 +3762,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D200">
-        <v>2.902634382247925</v>
+        <v>2.890832185745239</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3776,7 +3776,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D201">
-        <v>1.52683424949646</v>
+        <v>2.103972911834717</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3790,7 +3790,7 @@
         <v>25.10000038146973</v>
       </c>
       <c r="D202">
-        <v>21.078369140625</v>
+        <v>21.13559532165527</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3804,7 +3804,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D203">
-        <v>2.973902940750122</v>
+        <v>2.481001853942871</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -3818,7 +3818,7 @@
         <v>15.60000038146973</v>
       </c>
       <c r="D204">
-        <v>3.001867055892944</v>
+        <v>2.242912530899048</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -3832,7 +3832,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D205">
-        <v>2.075939416885376</v>
+        <v>1.647485971450806</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -3846,7 +3846,7 @@
         <v>20</v>
       </c>
       <c r="D206">
-        <v>14.46864986419678</v>
+        <v>13.7664270401001</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -3860,7 +3860,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D207">
-        <v>1.944706439971924</v>
+        <v>0.5369871258735657</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -3874,7 +3874,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D208">
-        <v>2.578204870223999</v>
+        <v>1.873537302017212</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -3888,7 +3888,7 @@
         <v>2.5</v>
       </c>
       <c r="D209">
-        <v>1.037842750549316</v>
+        <v>2.278720140457153</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -3902,7 +3902,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D210">
-        <v>1.671691656112671</v>
+        <v>1.867818355560303</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -3916,7 +3916,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D211">
-        <v>3.694161415100098</v>
+        <v>3.464101552963257</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -3930,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="D212">
-        <v>3.567829370498657</v>
+        <v>3.23797869682312</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -3944,7 +3944,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="D213">
-        <v>9.064760208129883</v>
+        <v>8.955085754394531</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -3958,7 +3958,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D214">
-        <v>2.928724050521851</v>
+        <v>2.453910350799561</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -3972,7 +3972,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D215">
-        <v>2.219810724258423</v>
+        <v>2.239590167999268</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -3986,7 +3986,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D216">
-        <v>2.849280118942261</v>
+        <v>3.678046464920044</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4000,7 +4000,7 @@
         <v>4.5</v>
       </c>
       <c r="D217">
-        <v>7.407291889190674</v>
+        <v>6.973652839660645</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4014,7 +4014,7 @@
         <v>2</v>
       </c>
       <c r="D218">
-        <v>1.514327645301819</v>
+        <v>1.444949388504028</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4028,7 +4028,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D219">
-        <v>2.554635524749756</v>
+        <v>2.401869773864746</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4042,7 +4042,7 @@
         <v>5</v>
       </c>
       <c r="D220">
-        <v>1.794990301132202</v>
+        <v>2.208431005477905</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4056,7 +4056,7 @@
         <v>2.5</v>
       </c>
       <c r="D221">
-        <v>3.421236038208008</v>
+        <v>3.67406964302063</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4070,7 +4070,7 @@
         <v>41</v>
       </c>
       <c r="D222">
-        <v>27.99596786499023</v>
+        <v>25.1613941192627</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4084,7 +4084,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D223">
-        <v>4.520795822143555</v>
+        <v>3.932571411132812</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4098,7 +4098,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D224">
-        <v>3.29735803604126</v>
+        <v>2.316754579544067</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4112,7 +4112,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D225">
-        <v>2.686877489089966</v>
+        <v>2.977766036987305</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4126,7 +4126,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D226">
-        <v>2.115523099899292</v>
+        <v>3.214027166366577</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4140,7 +4140,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D227">
-        <v>8.053013801574707</v>
+        <v>8.746471405029297</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4154,7 +4154,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D228">
-        <v>2.253017663955688</v>
+        <v>2.130661249160767</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4168,7 +4168,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D229">
-        <v>3.485007524490356</v>
+        <v>2.862147808074951</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4182,7 +4182,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D230">
-        <v>2.112876653671265</v>
+        <v>1.840916872024536</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4196,7 +4196,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D231">
-        <v>3.790871620178223</v>
+        <v>3.076922416687012</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4210,7 +4210,7 @@
         <v>2.5</v>
       </c>
       <c r="D232">
-        <v>3.463638305664062</v>
+        <v>3.494747877120972</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4224,7 +4224,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D233">
-        <v>2.578238248825073</v>
+        <v>2.395451307296753</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4238,7 +4238,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D234">
-        <v>1.227957248687744</v>
+        <v>0.7979605793952942</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4252,7 +4252,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D235">
-        <v>2.423205614089966</v>
+        <v>3.353044033050537</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4266,7 +4266,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D236">
-        <v>2.767346620559692</v>
+        <v>2.935661315917969</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4280,7 +4280,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D237">
-        <v>3.91420841217041</v>
+        <v>3.411410570144653</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4294,7 +4294,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D238">
-        <v>3.798624753952026</v>
+        <v>3.013448238372803</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4308,7 +4308,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D239">
-        <v>2.521663904190063</v>
+        <v>3.160760164260864</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4322,7 +4322,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D240">
-        <v>2.725393533706665</v>
+        <v>3.177374839782715</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4336,7 +4336,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D241">
-        <v>3.192995309829712</v>
+        <v>2.194111824035645</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4350,7 +4350,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D242">
-        <v>2.377224445343018</v>
+        <v>2.732897281646729</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4364,7 +4364,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D243">
-        <v>1.535632610321045</v>
+        <v>2.288926362991333</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4378,7 +4378,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D244">
-        <v>9.722423553466797</v>
+        <v>8.999181747436523</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4392,7 +4392,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D245">
-        <v>2.182995557785034</v>
+        <v>2.218131065368652</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4406,7 +4406,7 @@
         <v>14.80000019073486</v>
       </c>
       <c r="D246">
-        <v>16.54809379577637</v>
+        <v>15.21870040893555</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4420,7 +4420,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D247">
-        <v>2.680019617080688</v>
+        <v>2.037550926208496</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4434,7 +4434,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D248">
-        <v>2.76022744178772</v>
+        <v>2.818312406539917</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4448,7 +4448,7 @@
         <v>2</v>
       </c>
       <c r="D249">
-        <v>2.012698650360107</v>
+        <v>0.5380311608314514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4462,7 +4462,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D250">
-        <v>2.190419673919678</v>
+        <v>1.784334659576416</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4476,7 +4476,7 @@
         <v>3.5</v>
       </c>
       <c r="D251">
-        <v>3.202754259109497</v>
+        <v>3.074980020523071</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4490,7 +4490,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D252">
-        <v>2.666168689727783</v>
+        <v>2.274517059326172</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4504,7 +4504,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D253">
-        <v>3.882700204849243</v>
+        <v>3.901212215423584</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4518,7 +4518,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="D254">
-        <v>20.45360946655273</v>
+        <v>22.40743255615234</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4532,7 +4532,7 @@
         <v>33.09999847412109</v>
       </c>
       <c r="D255">
-        <v>30.42430877685547</v>
+        <v>28.91393852233887</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4546,7 +4546,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D256">
-        <v>3.481663465499878</v>
+        <v>2.234758615493774</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4560,7 +4560,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D257">
-        <v>2.137167453765869</v>
+        <v>2.803206205368042</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4574,7 +4574,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D258">
-        <v>1.403964281082153</v>
+        <v>2.042015314102173</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4588,7 +4588,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D259">
-        <v>3.538092374801636</v>
+        <v>3.231281995773315</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4602,7 +4602,7 @@
         <v>16.5</v>
       </c>
       <c r="D260">
-        <v>2.746058702468872</v>
+        <v>2.700455904006958</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4616,7 +4616,7 @@
         <v>5</v>
       </c>
       <c r="D261">
-        <v>2.545591831207275</v>
+        <v>2.26889967918396</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4630,7 +4630,7 @@
         <v>6</v>
       </c>
       <c r="D262">
-        <v>4.024129390716553</v>
+        <v>3.792338609695435</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4644,7 +4644,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D263">
-        <v>4.335948467254639</v>
+        <v>4.209196090698242</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4658,7 +4658,7 @@
         <v>3.5</v>
       </c>
       <c r="D264">
-        <v>2.217219591140747</v>
+        <v>2.120004415512085</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4672,7 +4672,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D265">
-        <v>1.836788415908813</v>
+        <v>1.749358892440796</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4686,7 +4686,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D266">
-        <v>2.960088968276978</v>
+        <v>2.199235200881958</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4700,7 +4700,7 @@
         <v>5.5</v>
       </c>
       <c r="D267">
-        <v>2.643778562545776</v>
+        <v>2.362658500671387</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4714,7 +4714,7 @@
         <v>29.20000076293945</v>
       </c>
       <c r="D268">
-        <v>26.02939987182617</v>
+        <v>21.85109710693359</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4728,7 +4728,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D269">
-        <v>3.635730028152466</v>
+        <v>2.123627662658691</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4742,7 +4742,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D270">
-        <v>3.139051198959351</v>
+        <v>2.724122285842896</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4756,7 +4756,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D271">
-        <v>2.212454795837402</v>
+        <v>2.297350168228149</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4770,7 +4770,7 @@
         <v>10.30000019073486</v>
       </c>
       <c r="D272">
-        <v>8.968410491943359</v>
+        <v>9.505256652832031</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4784,7 +4784,7 @@
         <v>7.5</v>
       </c>
       <c r="D273">
-        <v>10.96767616271973</v>
+        <v>10.799560546875</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4798,7 +4798,7 @@
         <v>3</v>
       </c>
       <c r="D274">
-        <v>2.763593435287476</v>
+        <v>2.67361307144165</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -4812,7 +4812,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D275">
-        <v>2.821464776992798</v>
+        <v>3.261873483657837</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -4826,7 +4826,7 @@
         <v>3.5</v>
       </c>
       <c r="D276">
-        <v>1.834421157836914</v>
+        <v>2.297815561294556</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -4840,7 +4840,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D277">
-        <v>2.096232891082764</v>
+        <v>1.231069087982178</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -4854,7 +4854,7 @@
         <v>3.5</v>
       </c>
       <c r="D278">
-        <v>2.241092443466187</v>
+        <v>2.251132249832153</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -4868,7 +4868,7 @@
         <v>31.29999923706055</v>
       </c>
       <c r="D279">
-        <v>25.31107521057129</v>
+        <v>24.83168029785156</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -4882,7 +4882,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D280">
-        <v>1.834781408309937</v>
+        <v>1.606114625930786</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -4896,7 +4896,7 @@
         <v>2</v>
       </c>
       <c r="D281">
-        <v>2.122016906738281</v>
+        <v>0.8604660034179688</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -4910,7 +4910,7 @@
         <v>1</v>
       </c>
       <c r="D282">
-        <v>3.750141620635986</v>
+        <v>2.97906494140625</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -4924,7 +4924,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D283">
-        <v>1.927919149398804</v>
+        <v>2.197308301925659</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -4938,7 +4938,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D284">
-        <v>2.856754064559937</v>
+        <v>3.215352773666382</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -4952,7 +4952,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D285">
-        <v>2.851469755172729</v>
+        <v>2.429394960403442</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -4966,7 +4966,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D286">
-        <v>2.16187310218811</v>
+        <v>2.024359703063965</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -4980,7 +4980,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D287">
-        <v>3.239156484603882</v>
+        <v>3.43207049369812</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -4994,7 +4994,7 @@
         <v>7</v>
       </c>
       <c r="D288">
-        <v>2.437632322311401</v>
+        <v>2.683151960372925</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5008,7 +5008,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D289">
-        <v>1.885111331939697</v>
+        <v>1.877229928970337</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5022,7 +5022,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D290">
-        <v>2.606139183044434</v>
+        <v>3.011713266372681</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5036,7 +5036,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D291">
-        <v>2.306351900100708</v>
+        <v>2.200025796890259</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5050,7 +5050,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D292">
-        <v>3.281697750091553</v>
+        <v>3.379874467849731</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5064,7 +5064,7 @@
         <v>7.5</v>
       </c>
       <c r="D293">
-        <v>2.061609983444214</v>
+        <v>3.265760183334351</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5078,7 +5078,7 @@
         <v>14.89999961853027</v>
       </c>
       <c r="D294">
-        <v>10.26607990264893</v>
+        <v>11.51055335998535</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5092,7 +5092,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D295">
-        <v>2.496091842651367</v>
+        <v>2.255522727966309</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5106,7 +5106,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D296">
-        <v>2.958390474319458</v>
+        <v>3.333348989486694</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5120,7 +5120,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D297">
-        <v>4.422364711761475</v>
+        <v>3.693489789962769</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5134,7 +5134,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D298">
-        <v>2.374439239501953</v>
+        <v>2.740529775619507</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5148,7 +5148,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D299">
-        <v>2.376483201980591</v>
+        <v>2.378944396972656</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5162,7 +5162,7 @@
         <v>30.5</v>
       </c>
       <c r="D300">
-        <v>17.8594856262207</v>
+        <v>18.35699462890625</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5176,7 +5176,7 @@
         <v>4.5</v>
       </c>
       <c r="D301">
-        <v>3.359418630599976</v>
+        <v>3.151384115219116</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5190,7 +5190,7 @@
         <v>5</v>
       </c>
       <c r="D302">
-        <v>2.752120018005371</v>
+        <v>2.18299674987793</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5204,7 +5204,7 @@
         <v>19.29999923706055</v>
       </c>
       <c r="D303">
-        <v>21.46444702148438</v>
+        <v>21.58480072021484</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5218,7 +5218,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D304">
-        <v>2.546306133270264</v>
+        <v>2.328750133514404</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5232,7 +5232,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D305">
-        <v>2.119559288024902</v>
+        <v>2.748816251754761</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5246,7 +5246,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D306">
-        <v>2.131330013275146</v>
+        <v>2.309697389602661</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5260,7 +5260,7 @@
         <v>10.89999961853027</v>
       </c>
       <c r="D307">
-        <v>2.970449924468994</v>
+        <v>3.039530277252197</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5274,7 +5274,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D308">
-        <v>3.010757684707642</v>
+        <v>2.261522769927979</v>
       </c>
     </row>
   </sheetData>
